--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108091</v>
+        <v>108104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108091</v>
+        <v>108104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108091</v>
+        <v>108104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108104</v>
+        <v>108105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108104</v>
+        <v>108105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108104</v>
+        <v>108105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
